--- a/annotated_data/mcmaster_reddit_part_1.xlsx
+++ b/annotated_data/mcmaster_reddit_part_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donyazolfaghari/Documents/Computer science/Winter 2025/CS 4NL3/ASSIGNMENTS/Final Project/annotation (others)/group18/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365-my.sharepoint.com/personal/guz38_mcmaster_ca/Documents/COMPSCI 4NL3/cs4nl-final-project/annotated_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2539BE95-EE36-A948-9CE1-58C0887A4489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2539BE95-EE36-A948-9CE1-58C0887A4489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E315C58-7DED-4B96-9CAF-AF0D8B69B6CB}"/>
   <bookViews>
-    <workbookView xWindow="16100" yWindow="500" windowWidth="12700" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8050" yWindow="1660" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -980,12 +980,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="70.5" customWidth="1"/>
+    <col min="2" max="2" width="70.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>172</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>173</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>174</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>175</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>176</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>177</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>178</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>179</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="320" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>180</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>181</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="240" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>182</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>183</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>184</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>185</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>186</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>187</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>188</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>189</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>190</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="208" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="203" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>191</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>192</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>193</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>194</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>195</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>196</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>197</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>198</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>199</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>200</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>201</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>202</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>203</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>204</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>205</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>206</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>207</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>208</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>209</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>210</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>211</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>212</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>213</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>214</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>215</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>216</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>217</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>218</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>219</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>220</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>221</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="261" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>222</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="380" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="377" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>223</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>224</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>225</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="224" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="203" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>226</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>227</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>228</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="395" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="377" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>229</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>230</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="176" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>231</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>232</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>233</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>234</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>235</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>236</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>237</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>238</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>239</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>240</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>241</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>242</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="304" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>243</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>244</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>245</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="240" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="232" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>246</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>247</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>248</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>249</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>250</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>251</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>252</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="144" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>253</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>254</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>255</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>256</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>257</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="174" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>258</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>259</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>260</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>261</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>262</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>263</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>264</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>265</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>266</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>267</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>268</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>269</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>270</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>271</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>272</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>273</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>274</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>275</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="176" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>276</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>277</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>278</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>279</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="304" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>280</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>281</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>282</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>283</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>284</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>285</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>286</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" ht="203" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>287</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>288</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>289</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>290</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>291</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>292</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>293</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>294</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>295</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>296</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>297</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>298</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>299</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>300</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>301</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>302</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>303</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>304</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>305</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>306</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>307</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>308</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>309</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>310</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>311</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>312</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="304" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>313</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>314</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>315</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>316</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>317</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>318</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>319</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>320</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="304" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>321</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>322</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>323</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>324</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="320" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>325</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>326</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>327</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="144" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>328</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>329</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>330</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>331</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>332</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>333</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>334</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>335</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>336</v>
       </c>
@@ -2811,15 +2811,18 @@
         <v>178</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>337</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="C167" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>338</v>
       </c>
@@ -2830,7 +2833,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>339</v>
       </c>
@@ -2841,7 +2844,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>340</v>
       </c>
@@ -2852,7 +2855,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>341</v>
       </c>
@@ -2863,7 +2866,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>342</v>
       </c>
@@ -2874,7 +2877,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>343</v>
       </c>
@@ -2885,7 +2888,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>344</v>
       </c>
